--- a/marketing_forms/031_loyalty_rewards_form--marketing_forms.xlsx
+++ b/marketing_forms/031_loyalty_rewards_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>loyalty_rewards_form</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>loyalty_rewards_form</t>
+          <t>Customer's Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>Customer's Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>customer_phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Customer's Phone Number</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,64 +589,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>customer_store_visit_count</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>Number of Customer Store Visits</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_store_visit_count</t>
+          <t>reward_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customer_store_visit_count</t>
+          <t>Reward Type</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>reward_type</t>
+          <t>store</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>reward_type</t>
+          <t>Store Location</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>store</t>
+          <t>points_earned</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>store</t>
+          <t>Points Earned</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,87 +681,87 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>points_earned</t>
+          <t>customer_address</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>points_earned</t>
+          <t>Customer's Address</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>customer_address</t>
+          <t>reward_status</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>customer_address</t>
+          <t>Reward Status</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reward_status</t>
+          <t>customer_last_visit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>reward_status</t>
+          <t>Customer's Last Visit Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>customer_first_visit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>Customer's First Visit Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,87 +773,87 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>reward_date</t>
+          <t>reward_expiration</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>reward_date</t>
+          <t>Reward Expiration Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>customer_store_last_visit_date</t>
+          <t>customer_total_visits</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>customer_store_last_visit_date</t>
+          <t>Customer's Total Visits</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>customer_first_visit_date</t>
+          <t>customer_reward_balance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>customer_first_visit_date</t>
+          <t>Customer's Reward Balance</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>reward_expiration_date</t>
+          <t>customer_total_visits_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>reward_expiration_date</t>
+          <t>Customer Total Visits 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,41 +865,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>customer_reward_balance</t>
+          <t>reward_balance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>customer_reward_balance</t>
+          <t>Reward Balance</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>customer_last_visit</t>
+          <t>customer_phone_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>customer_last_visit</t>
+          <t>Customer's Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,179 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>customer_total_visits</t>
+          <t>store_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>customer_total_visits</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>customer_first_visit</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>customer_first_visit</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>reward_balance</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>reward_balance</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>customer_phone</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>customer_phone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_email</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>customer_email</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>customer_address</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>customer_address</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>reward_status</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>reward_status</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1136,7 +975,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>loyalty points</t>
+          <t>Loyalty points</t>
         </is>
       </c>
     </row>
@@ -1153,7 +992,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>free gift</t>
+          <t>Free Gift</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1009,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>free product</t>
+          <t>Free Product</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1026,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>free gift card</t>
+          <t>Free Gift Card</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1043,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1060,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>awarded</t>
+          <t>Awarded</t>
         </is>
       </c>
     </row>
@@ -1238,58 +1077,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>reward_status_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>reward_status_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>awarded</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>awarded</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>reward_status_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>expired</t>
+          <t>Expired</t>
         </is>
       </c>
     </row>
